--- a/ta/ind.xlsx
+++ b/ta/ind.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25128"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\r\ta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\■\ta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{505D9627-E1FA-4E9B-B2A2-0EB2CA979B52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90EA2303-3105-4810-ADF4-D2A51FD3A12D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1230,13 +1230,13 @@
     <tableColumn id="7" xr3:uid="{D2BA039E-10A9-414D-B17D-FB19508FCEB4}" name="tt" dataDxfId="9"/>
     <tableColumn id="8" xr3:uid="{F554DD79-31B8-4647-A2C7-D6C5404040D4}" name="tc2" dataDxfId="8"/>
     <tableColumn id="9" xr3:uid="{017A7E09-53A8-4CEF-AE3F-5E6ECC9E1B62}" name="mio" dataDxfId="7"/>
-    <tableColumn id="19" xr3:uid="{26932533-7871-4D21-AB8A-65FE974F09E9}" name="mv" dataDxfId="0"/>
-    <tableColumn id="10" xr3:uid="{ABD9386F-EEDE-4C88-907E-3AEF79082283}" name="pc" dataDxfId="6"/>
-    <tableColumn id="11" xr3:uid="{FEAF1EE7-AB95-4690-86A4-73E18ED40FA6}" name="js" dataDxfId="5"/>
-    <tableColumn id="16" xr3:uid="{A783F806-3E82-4F72-A8D5-5CA8B2D7AFF6}" name="js2" dataDxfId="4"/>
-    <tableColumn id="12" xr3:uid="{2FB839E2-A84F-4D1B-89CF-1FFC3B114A08}" name="py" dataDxfId="3"/>
-    <tableColumn id="15" xr3:uid="{38EF0105-FED7-4CB6-9E15-CB2F32D3AB5C}" name="py2" dataDxfId="2"/>
-    <tableColumn id="14" xr3:uid="{7BE96C0B-1FFA-45C1-809C-F3548F119714}" name="mat" dataDxfId="1"/>
+    <tableColumn id="19" xr3:uid="{26932533-7871-4D21-AB8A-65FE974F09E9}" name="mv" dataDxfId="6"/>
+    <tableColumn id="10" xr3:uid="{ABD9386F-EEDE-4C88-907E-3AEF79082283}" name="pc" dataDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{FEAF1EE7-AB95-4690-86A4-73E18ED40FA6}" name="js" dataDxfId="4"/>
+    <tableColumn id="16" xr3:uid="{A783F806-3E82-4F72-A8D5-5CA8B2D7AFF6}" name="js2" dataDxfId="3"/>
+    <tableColumn id="12" xr3:uid="{2FB839E2-A84F-4D1B-89CF-1FFC3B114A08}" name="py" dataDxfId="2"/>
+    <tableColumn id="15" xr3:uid="{38EF0105-FED7-4CB6-9E15-CB2F32D3AB5C}" name="py2" dataDxfId="1"/>
+    <tableColumn id="14" xr3:uid="{7BE96C0B-1FFA-45C1-809C-F3548F119714}" name="mat" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
